--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487858_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487858_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>T. SAGNA</t>
+          <t>O. ARDANZA BERNAOLA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9206</v>
+        <v>3.3645</v>
       </c>
       <c r="E2" t="n">
-        <v>4.1846</v>
+        <v>2.9015</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2641</v>
+        <v>0.463</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3487</v>
+        <v>0.4791</v>
       </c>
       <c r="H2" t="n">
-        <v>1.0426</v>
+        <v>-0.9913</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.694</v>
+        <v>1.4704</v>
       </c>
       <c r="J2" t="n">
-        <v>2.9207</v>
+        <v>1.3692</v>
       </c>
       <c r="K2" t="n">
-        <v>2.7247</v>
+        <v>0.1151</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1959</v>
+        <v>1.254</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.572</v>
+        <v>-0.8901</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.6821</v>
+        <v>-1.1064</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.8899</v>
+        <v>0.2164</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2081</v>
+        <v>0.8325</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2893</v>
+        <v>0.8325</v>
       </c>
       <c r="S2" t="n">
-        <v>3.3638</v>
+        <v>0.7439</v>
       </c>
       <c r="T2" t="n">
-        <v>3.1152</v>
+        <v>0.3648</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2486</v>
+        <v>0.3791</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.309</v>
       </c>
       <c r="W2" t="n">
-        <v>0.23</v>
+        <v>1.1675</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.23</v>
+        <v>0.1415</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. NIANG NDONGO</t>
+          <t>P. BADJI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2052</v>
+        <v>2.5249</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5203</v>
+        <v>1.6265</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3151</v>
+        <v>0.8984</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.6594</v>
+        <v>2.2408</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2811</v>
+        <v>1.3582</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.9405</v>
+        <v>0.8826000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>2.3289</v>
+        <v>2.7961</v>
       </c>
       <c r="K3" t="n">
-        <v>2.3469</v>
+        <v>2.1299</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.018</v>
+        <v>0.6662</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.9884</v>
+        <v>-0.5553</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.0658</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.9225</v>
+        <v>0.2164</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.0812</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q3" t="n">
-        <v>-4.1624</v>
+        <v>-1.0406</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0812</v>
+        <v>0.4162</v>
       </c>
       <c r="S3" t="n">
-        <v>2.3017</v>
+        <v>0.4131</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6212</v>
+        <v>-0.129</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6805</v>
+        <v>0.5422</v>
       </c>
       <c r="V3" t="n">
-        <v>3.6441</v>
+        <v>0.4953</v>
       </c>
       <c r="W3" t="n">
-        <v>3.7325</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.08840000000000001</v>
+        <v>0.4953</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>O. ARDANZA BERNAOLA</t>
+          <t>M. NIANG NDONGO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1399</v>
+        <v>2.2686</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7944</v>
+        <v>2.8774</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3456</v>
+        <v>-0.6087</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4791</v>
+        <v>-0.6594</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.9913</v>
+        <v>0.2811</v>
       </c>
       <c r="I4" t="n">
-        <v>1.4704</v>
+        <v>-0.9405</v>
       </c>
       <c r="J4" t="n">
-        <v>1.3692</v>
+        <v>2.3289</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1151</v>
+        <v>2.3469</v>
       </c>
       <c r="L4" t="n">
-        <v>1.254</v>
+        <v>-0.018</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8901</v>
+        <v>-2.9884</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.1064</v>
+        <v>-2.0658</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2164</v>
+        <v>-0.9225</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8325</v>
+        <v>-2.0812</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-4.1624</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8325</v>
+        <v>2.0812</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5193</v>
+        <v>1.3652</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2577</v>
+        <v>0.9782</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2616</v>
+        <v>0.3869</v>
       </c>
       <c r="V4" t="n">
-        <v>1.309</v>
+        <v>3.6441</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1675</v>
+        <v>3.7325</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1415</v>
+        <v>-0.08840000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. BADJI</t>
+          <t>T. SAGNA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.0225</v>
+        <v>1.9918</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9479</v>
+        <v>2.2558</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0746</v>
+        <v>-0.2641</v>
       </c>
       <c r="G5" t="n">
-        <v>2.2408</v>
+        <v>0.3487</v>
       </c>
       <c r="H5" t="n">
-        <v>1.3582</v>
+        <v>1.0426</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8826000000000001</v>
+        <v>-0.694</v>
       </c>
       <c r="J5" t="n">
-        <v>2.7961</v>
+        <v>2.9207</v>
       </c>
       <c r="K5" t="n">
-        <v>2.1299</v>
+        <v>2.7247</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6662</v>
+        <v>0.1959</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5553</v>
+        <v>-2.572</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7717000000000001</v>
+        <v>-1.6821</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2164</v>
+        <v>-0.8899</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.6244</v>
+        <v>0.2081</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4162</v>
+        <v>2.2893</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9108000000000001</v>
+        <v>1.4349</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1924</v>
+        <v>1.1864</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7183</v>
+        <v>0.2486</v>
       </c>
       <c r="V5" t="n">
-        <v>0.4953</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="X5" t="n">
-        <v>0.4953</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4378</v>
+        <v>0.6917</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7020999999999999</v>
+        <v>-0.5949</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1398</v>
+        <v>1.2866</v>
       </c>
       <c r="G6" t="n">
         <v>-0.2123</v>
@@ -922,13 +922,13 @@
         <v>0.6244</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.045</v>
+        <v>0.2089</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.06519999999999999</v>
+        <v>0.0419</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0202</v>
+        <v>0.167</v>
       </c>
       <c r="V6" t="n">
         <v>0.0708</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. OLAIZOLA GARIN</t>
+          <t>A. MONCANUT MORE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2352</v>
+        <v>0.3578</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8068</v>
+        <v>2.2599</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5716</v>
+        <v>-1.9022</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9153</v>
+        <v>0.4473</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3112</v>
+        <v>-1.388</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6041</v>
+        <v>1.8353</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.2539</v>
+        <v>3.999</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4605</v>
+        <v>1.2044</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7144</v>
+        <v>2.7946</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6614</v>
+        <v>-3.5518</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7717000000000001</v>
+        <v>-2.5925</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1102</v>
+        <v>-0.9593</v>
       </c>
       <c r="P7" t="n">
-        <v>1.0406</v>
+        <v>0.6244</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R7" t="n">
-        <v>1.0406</v>
+        <v>1.6649</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5904</v>
+        <v>-0.077</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7829</v>
+        <v>0.0091</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1925</v>
+        <v>-0.0861</v>
       </c>
       <c r="V7" t="n">
-        <v>0.23</v>
+        <v>-0.6368</v>
       </c>
       <c r="W7" t="n">
-        <v>0.23</v>
+        <v>-0.7076</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.0708</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. MONCANUT MORE</t>
+          <t>M. OLAIZOLA GARIN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.705</v>
+        <v>0.3094</v>
       </c>
       <c r="E8" t="n">
-        <v>1.4027</v>
+        <v>-0.0567</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.1077</v>
+        <v>0.3661</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4473</v>
+        <v>-0.9153</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.388</v>
+        <v>-0.3112</v>
       </c>
       <c r="I8" t="n">
-        <v>1.8353</v>
+        <v>-0.6041</v>
       </c>
       <c r="J8" t="n">
-        <v>3.999</v>
+        <v>-0.2539</v>
       </c>
       <c r="K8" t="n">
-        <v>1.2044</v>
+        <v>0.4605</v>
       </c>
       <c r="L8" t="n">
-        <v>2.7946</v>
+        <v>-0.7144</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.5518</v>
+        <v>-0.6614</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.5925</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9593</v>
+        <v>0.1102</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6244</v>
+        <v>1.0406</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6649</v>
+        <v>1.0406</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1398</v>
+        <v>-0.0458</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8482</v>
+        <v>-0.0328</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2916</v>
+        <v>-0.013</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6368</v>
+        <v>0.23</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.7076</v>
+        <v>0.23</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0708</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. ACHA CORTABARRIA</t>
+          <t>I. MIRANDA GARCIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3249</v>
+        <v>-1.8018</v>
       </c>
       <c r="E9" t="n">
-        <v>1.7743</v>
+        <v>-0.483</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.0993</v>
+        <v>-1.3188</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.1949</v>
+        <v>-0.5051</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.5905</v>
+        <v>-1.1321</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.6044</v>
+        <v>0.627</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.0759</v>
+        <v>0.6462</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2834</v>
+        <v>0.0192</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.3594</v>
+        <v>0.627</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.119</v>
+        <v>-1.1513</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.874</v>
+        <v>-1.1513</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.245</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.2487</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2893</v>
+        <v>0.4162</v>
       </c>
       <c r="S9" t="n">
-        <v>1.1437</v>
+        <v>-0.0886</v>
       </c>
       <c r="T9" t="n">
-        <v>0.972</v>
+        <v>-0.0886</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1716</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>0.4776</v>
+        <v>-0.5838</v>
       </c>
       <c r="W9" t="n">
-        <v>2.9188</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.4412</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. MIRANDA GARCIA</t>
+          <t>A. ACHA CORTABARRIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9089</v>
+        <v>-2.0369</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5901</v>
+        <v>1.2386</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3188</v>
+        <v>-3.2754</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.5051</v>
+        <v>-4.1949</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.1321</v>
+        <v>-1.5905</v>
       </c>
       <c r="I10" t="n">
-        <v>0.627</v>
+        <v>-2.6044</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6462</v>
+        <v>-1.0759</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0192</v>
+        <v>0.2834</v>
       </c>
       <c r="L10" t="n">
-        <v>0.627</v>
+        <v>-1.3594</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1513</v>
+        <v>-3.119</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.1513</v>
+        <v>-1.874</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>-1.245</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6244</v>
+        <v>1.2487</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4162</v>
+        <v>2.2893</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1957</v>
+        <v>0.4317</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1957</v>
+        <v>0.4363</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>-0.0045</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5838</v>
+        <v>0.4776</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.9188</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5838</v>
+        <v>-2.4412</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.8784</v>
+        <v>-2.322</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.6813</v>
+        <v>-2.3598</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.197</v>
+        <v>0.0378</v>
       </c>
       <c r="G11" t="n">
         <v>-5.1116</v>
@@ -1312,13 +1312,13 @@
         <v>2.4974</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.002</v>
+        <v>0.5544</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0619</v>
+        <v>0.3834</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0639</v>
+        <v>0.171</v>
       </c>
       <c r="V11" t="n">
         <v>0.7784</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.2913</v>
+        <v>-2.6674</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.5955</v>
+        <v>-3.0597</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3042</v>
+        <v>0.3923</v>
       </c>
       <c r="G12" t="n">
         <v>-2.88</v>
@@ -1390,13 +1390,13 @@
         <v>0.8325</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6309</v>
+        <v>-0.007</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.0514</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0437</v>
+        <v>0.0444</v>
       </c>
       <c r="V12" t="n">
         <v>1.4683</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.3552</v>
+        <v>-3.6535</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.2671</v>
+        <v>-3.6242</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0881</v>
+        <v>-0.0294</v>
       </c>
       <c r="G13" t="n">
         <v>-3.3661</v>
@@ -1468,13 +1468,13 @@
         <v>0.6244</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5728</v>
+        <v>0.1288</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6524</v>
+        <v>-0.0095</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0796</v>
+        <v>0.1383</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.9729000000000005</v>
+        <v>-0.9728999999999997</v>
       </c>
       <c r="E14" t="n">
-        <v>2.981300000000002</v>
+        <v>2.981400000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.9543</v>
+        <v>-3.9544</v>
       </c>
       <c r="G14" t="n">
         <v>-14.3288</v>
@@ -1534,7 +1534,7 @@
         <v>-16.1064</v>
       </c>
       <c r="O14" t="n">
-        <v>-3.7145</v>
+        <v>-3.714500000000001</v>
       </c>
       <c r="P14" t="n">
         <v>1.0406</v>
@@ -1546,19 +1546,19 @@
         <v>15.6089</v>
       </c>
       <c r="S14" t="n">
-        <v>5.062699999999999</v>
+        <v>5.062500000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>3.088799999999998</v>
+        <v>3.0888</v>
       </c>
       <c r="U14" t="n">
-        <v>1.9737</v>
+        <v>1.9739</v>
       </c>
       <c r="V14" t="n">
         <v>7.252899999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>8.968699999999998</v>
+        <v>8.9687</v>
       </c>
       <c r="X14" t="n">
         <v>-1.7158</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.9314</v>
+        <v>4.3575</v>
       </c>
       <c r="E15" t="n">
-        <v>4.0352</v>
+        <v>3.2852</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8962</v>
+        <v>1.0723</v>
       </c>
       <c r="G15" t="n">
         <v>3.6057</v>
@@ -1624,13 +1624,13 @@
         <v>1.2487</v>
       </c>
       <c r="S15" t="n">
-        <v>0.077</v>
+        <v>-0.497</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7763</v>
+        <v>0.0262</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6993</v>
+        <v>-0.5232</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>V. ORLOV STURMAN MAURIN</t>
+          <t>G. FERNANDEZ DIAZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.0949</v>
+        <v>3.5825</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1882</v>
+        <v>2.5429</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9068</v>
+        <v>1.0397</v>
       </c>
       <c r="G16" t="n">
-        <v>3.452</v>
+        <v>1.7173</v>
       </c>
       <c r="H16" t="n">
-        <v>2.3646</v>
+        <v>0.5098</v>
       </c>
       <c r="I16" t="n">
-        <v>1.0875</v>
+        <v>1.2075</v>
       </c>
       <c r="J16" t="n">
-        <v>2.8195</v>
+        <v>1.7991</v>
       </c>
       <c r="K16" t="n">
-        <v>2.6627</v>
+        <v>1.0937</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1568</v>
+        <v>0.7054</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6325</v>
+        <v>-0.0818</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2982</v>
+        <v>-0.5839</v>
       </c>
       <c r="O16" t="n">
-        <v>0.9307</v>
+        <v>0.5021</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.0406</v>
+        <v>1.2487</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.0406</v>
+        <v>1.2487</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.484</v>
+        <v>-0.1972</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7177</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2336</v>
+        <v>-0.1272</v>
       </c>
       <c r="V16" t="n">
-        <v>1.1675</v>
+        <v>0.8137</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1675</v>
+        <v>0.8137</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. FERNANDEZ DIAZ</t>
+          <t>V. ORLOV STURMAN MAURIN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.9088</v>
+        <v>3.1419</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2214</v>
+        <v>1.6168</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6874</v>
+        <v>1.5251</v>
       </c>
       <c r="G17" t="n">
-        <v>1.7173</v>
+        <v>3.452</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5098</v>
+        <v>2.3646</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2075</v>
+        <v>1.0875</v>
       </c>
       <c r="J17" t="n">
-        <v>1.7991</v>
+        <v>2.8195</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0937</v>
+        <v>2.6627</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7054</v>
+        <v>0.1568</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0818</v>
+        <v>0.6325</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5839</v>
+        <v>-0.2982</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5021</v>
+        <v>0.9307</v>
       </c>
       <c r="P17" t="n">
-        <v>1.2487</v>
+        <v>-1.0406</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2487</v>
+        <v>1.0406</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.871</v>
+        <v>-0.4371</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3915</v>
+        <v>-0.2891</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4795</v>
+        <v>-0.148</v>
       </c>
       <c r="V17" t="n">
-        <v>0.8137</v>
+        <v>1.1675</v>
       </c>
       <c r="W17" t="n">
-        <v>0.8137</v>
+        <v>1.1675</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.6113</v>
+        <v>0.801</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9469</v>
+        <v>1.5183</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3356</v>
+        <v>-0.7173</v>
       </c>
       <c r="G18" t="n">
         <v>0.4737</v>
@@ -1858,13 +1858,13 @@
         <v>1.8731</v>
       </c>
       <c r="S18" t="n">
-        <v>0.659</v>
+        <v>-0.1513</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3229</v>
+        <v>-0.1057</v>
       </c>
       <c r="U18" t="n">
-        <v>0.336</v>
+        <v>-0.0456</v>
       </c>
       <c r="V18" t="n">
         <v>-0.3538</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.0221</v>
+        <v>0.73</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9248</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0974</v>
+        <v>0.1267</v>
       </c>
       <c r="G19" t="n">
         <v>0.0709</v>
@@ -1936,13 +1936,13 @@
         <v>1.8731</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4619</v>
+        <v>-0.754</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1924</v>
+        <v>-0.129</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6543</v>
+        <v>-0.625</v>
       </c>
       <c r="V19" t="n">
         <v>-0.4599</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>K. NAVARRO ARRUE</t>
+          <t>J. JIMÉNEZ GONZÁLEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3977</v>
+        <v>0.6341</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0762</v>
+        <v>1.0281</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3216</v>
+        <v>-0.394</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7292</v>
+        <v>3.4493</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1578</v>
+        <v>0.4245</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4286</v>
+        <v>3.0248</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2067</v>
+        <v>4.8171</v>
       </c>
       <c r="K20" t="n">
-        <v>0.921</v>
+        <v>1.7269</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.7144</v>
+        <v>3.0901</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5225</v>
+        <v>-1.3678</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2367</v>
+        <v>-1.3025</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2857</v>
+        <v>-0.0653</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2081</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-3.1218</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2081</v>
+        <v>2.4974</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5395</v>
+        <v>-0.7756999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1305</v>
+        <v>-0.4195</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4091</v>
+        <v>-0.3562</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-1.4152</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.2477</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. JIMÉNEZ GONZÁLEZ</t>
+          <t>K. NAVARRO ARRUE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2348</v>
+        <v>0.5342</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5995</v>
+        <v>0.1833</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3647</v>
+        <v>0.3509</v>
       </c>
       <c r="G21" t="n">
-        <v>3.4493</v>
+        <v>0.7292</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4245</v>
+        <v>1.1578</v>
       </c>
       <c r="I21" t="n">
-        <v>3.0248</v>
+        <v>-0.4286</v>
       </c>
       <c r="J21" t="n">
-        <v>4.8171</v>
+        <v>0.2067</v>
       </c>
       <c r="K21" t="n">
-        <v>1.7269</v>
+        <v>0.921</v>
       </c>
       <c r="L21" t="n">
-        <v>3.0901</v>
+        <v>-0.7144</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.3678</v>
+        <v>0.5225</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.3025</v>
+        <v>0.2367</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0653</v>
+        <v>0.2857</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.6244</v>
+        <v>0.2081</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.1218</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.4974</v>
+        <v>0.2081</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.175</v>
+        <v>-0.403</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8482</v>
+        <v>-0.0233</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3268</v>
+        <v>-0.3797</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.4152</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.2477</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1454</v>
+        <v>0.2041</v>
       </c>
       <c r="E22" t="n">
         <v>-0.1957</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3411</v>
+        <v>0.3999</v>
       </c>
       <c r="G22" t="n">
         <v>0.2367</v>
@@ -2170,13 +2170,13 @@
         <v>0.2081</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2995</v>
+        <v>-0.2407</v>
       </c>
       <c r="T22" t="n">
         <v>-0.1957</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1037</v>
+        <v>-0.045</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.8075</v>
+        <v>-0.5051</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.4678</v>
+        <v>-0.2535</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3397</v>
+        <v>-0.2516</v>
       </c>
       <c r="G23" t="n">
         <v>2.706</v>
@@ -2248,13 +2248,13 @@
         <v>1.6649</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7861</v>
+        <v>-0.4838</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4567</v>
+        <v>-0.2424</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3294</v>
+        <v>-0.2414</v>
       </c>
       <c r="V23" t="n">
         <v>-0.23</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.5813</v>
+        <v>-1.5608</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7544999999999999</v>
+        <v>0.5402</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.3358</v>
+        <v>-2.101</v>
       </c>
       <c r="G24" t="n">
         <v>1.001</v>
@@ -2326,13 +2326,13 @@
         <v>1.0406</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2473</v>
+        <v>-0.2267</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1272</v>
+        <v>-0.0871</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3744</v>
+        <v>-0.1396</v>
       </c>
       <c r="V24" t="n">
         <v>-2.3351</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-9.1151</v>
+        <v>-9.077</v>
       </c>
       <c r="E26" t="n">
-        <v>-6.0814</v>
+        <v>-5.8671</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.0337</v>
+        <v>-3.2099</v>
       </c>
       <c r="G26" t="n">
         <v>-3.2652</v>
@@ -2482,13 +2482,13 @@
         <v>1.0406</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.7261</v>
+        <v>-0.6879</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.3729</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.1389</v>
+        <v>-0.3151</v>
       </c>
       <c r="V26" t="n">
         <v>-3.0427</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>0.9728999999999992</v>
+        <v>0.9727999999999977</v>
       </c>
       <c r="E27" t="n">
-        <v>3.9543</v>
+        <v>3.954300000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.981100000000001</v>
+        <v>-2.9813</v>
       </c>
       <c r="G27" t="n">
         <v>14.3288</v>
@@ -2530,7 +2530,7 @@
         <v>10.7571</v>
       </c>
       <c r="I27" t="n">
-        <v>3.571899999999999</v>
+        <v>3.571900000000001</v>
       </c>
       <c r="J27" t="n">
         <v>19.8212</v>
@@ -2548,7 +2548,7 @@
         <v>-5.3494</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.1428</v>
+        <v>-0.1427999999999998</v>
       </c>
       <c r="P27" t="n">
         <v>-1.0406</v>
@@ -2563,10 +2563,10 @@
         <v>-5.0625</v>
       </c>
       <c r="T27" t="n">
-        <v>-1.9739</v>
+        <v>-1.9737</v>
       </c>
       <c r="U27" t="n">
-        <v>-3.0887</v>
+        <v>-3.0889</v>
       </c>
       <c r="V27" t="n">
         <v>-7.253</v>
